--- a/data/vessels/2026-10-26.xlsx
+++ b/data/vessels/2026-10-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="458229" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB97EC2-51E6-4CA4-B837-44B311F67E35}"/>
+  <xr:revisionPtr revIDLastSave="459096" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1AFFF46-4A26-4E64-B6ED-A44E5BA6024D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="221">
   <si>
     <t>Harbor</t>
   </si>
@@ -113,343 +113,421 @@
     <t>Yang Ming</t>
   </si>
   <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>198E</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>RED CLOUD</t>
+  </si>
+  <si>
+    <t>KRF</t>
+  </si>
+  <si>
+    <t>833rd Trans Bn Sddc</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>129W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>ACGI</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
     <t>PN3</t>
   </si>
   <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>010W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>015E/016W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>2606E/2606W</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>136W</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK642R</t>
+  </si>
+  <si>
+    <t>SANTA RITA</t>
+  </si>
+  <si>
+    <t>642E</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640W</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
+    <t>FP22633C</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>26E</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>Hyundai Glovis</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>198E</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>RED CLOUD</t>
-  </si>
-  <si>
-    <t>KRF</t>
-  </si>
-  <si>
-    <t>833rd Trans Bn Sddc</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>129W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>ACGI</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>010W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>015E/016W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN06/CPN07</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>2606E/2606W</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>136W</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK642R</t>
-  </si>
-  <si>
-    <t>SANTA RITA</t>
-  </si>
-  <si>
-    <t>642E</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640W</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
-    <t>FP22633C</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>26E</t>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>011W</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>46E</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>COSCO SANTOS</t>
+  </si>
+  <si>
+    <t>NOCC ADRIATIC</t>
+  </si>
+  <si>
+    <t>KW667</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>CORNEILLE</t>
+  </si>
+  <si>
+    <t>14E</t>
   </si>
   <si>
     <t>BUDAPEST EXPRESS</t>
@@ -458,106 +536,22 @@
     <t>641E</t>
   </si>
   <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC644R</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC645R</t>
-  </si>
-  <si>
-    <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>011W</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK644R</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>LOTUS A</t>
   </si>
   <si>
     <t>SM MUMBAI</t>
   </si>
   <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>46E</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>NOCC ADRIATIC</t>
-  </si>
-  <si>
-    <t>KW667</t>
-  </si>
-  <si>
-    <t>Eukor</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
+    <t>GLOVIS LEGEND</t>
   </si>
   <si>
     <t>ONE MODERN</t>
@@ -566,9 +560,6 @@
     <t>83E</t>
   </si>
   <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
     <t>EVER STRONG</t>
   </si>
   <si>
@@ -596,124 +587,115 @@
     <t>MC639A</t>
   </si>
   <si>
+    <t>OOCL OAKLAND</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
     <t>YM MANDATE</t>
   </si>
   <si>
     <t>606E</t>
   </si>
   <si>
+    <t>THEBEN</t>
+  </si>
+  <si>
+    <t>ED617</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>MSC DESIREE</t>
+  </si>
+  <si>
+    <t>CMA CGM ARKANSAS</t>
+  </si>
+  <si>
+    <t>GLORIOUS ACE</t>
+  </si>
+  <si>
+    <t>113A</t>
+  </si>
+  <si>
+    <t>EVER MAGUS</t>
+  </si>
+  <si>
+    <t>1476-009E</t>
+  </si>
+  <si>
+    <t>HMM VANCOUVER</t>
+  </si>
+  <si>
+    <t>308E</t>
+  </si>
+  <si>
+    <t>EUPHONY ACE</t>
+  </si>
+  <si>
+    <t>166A</t>
+  </si>
+  <si>
+    <t>TOURMALINE ACE</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
+    <t>MAERSK SARNIA</t>
+  </si>
+  <si>
+    <t>643E</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>EVER SUMMIT</t>
+  </si>
+  <si>
+    <t>498-133E</t>
+  </si>
+  <si>
+    <t>SM SEOUL</t>
+  </si>
+  <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>159A</t>
+  </si>
+  <si>
+    <t>GLOVIS SUMMIT</t>
+  </si>
+  <si>
+    <t>APS Stevedoring</t>
+  </si>
+  <si>
+    <t>MSC ELISABETTA</t>
+  </si>
+  <si>
+    <t>MC640A</t>
+  </si>
+  <si>
+    <t>YM TROPHY</t>
+  </si>
+  <si>
+    <t>23E</t>
+  </si>
+  <si>
+    <t>WESTWOOD OLYMPIA</t>
+  </si>
+  <si>
+    <t>140E</t>
+  </si>
+  <si>
     <t>XIN ZHAN JIANG</t>
   </si>
   <si>
     <t>201N</t>
-  </si>
-  <si>
-    <t>OOCL OAKLAND</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>THEBEN</t>
-  </si>
-  <si>
-    <t>ED617</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>MSC DESIREE</t>
-  </si>
-  <si>
-    <t>CMA CGM ARKANSAS</t>
-  </si>
-  <si>
-    <t>HMM VANCOUVER</t>
-  </si>
-  <si>
-    <t>308E</t>
-  </si>
-  <si>
-    <t>GLORIOUS ACE</t>
-  </si>
-  <si>
-    <t>113A</t>
-  </si>
-  <si>
-    <t>EVER MAGUS</t>
-  </si>
-  <si>
-    <t>1476-009E</t>
-  </si>
-  <si>
-    <t>EUPHONY ACE</t>
-  </si>
-  <si>
-    <t>166A</t>
-  </si>
-  <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
-  </si>
-  <si>
-    <t>MAERSK SARNIA</t>
-  </si>
-  <si>
-    <t>643E</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>SANTA BARBARA</t>
-  </si>
-  <si>
-    <t>651E</t>
-  </si>
-  <si>
-    <t>EVER SUMMIT</t>
-  </si>
-  <si>
-    <t>498-133E</t>
-  </si>
-  <si>
-    <t>EVER SIGMA</t>
-  </si>
-  <si>
-    <t>499-144E</t>
-  </si>
-  <si>
-    <t>GLOVIS SUMMIT</t>
-  </si>
-  <si>
-    <t>APS Stevedoring</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>159A</t>
-  </si>
-  <si>
-    <t>MSC ELISABETTA</t>
-  </si>
-  <si>
-    <t>MC640A</t>
-  </si>
-  <si>
-    <t>YM TROPHY</t>
-  </si>
-  <si>
-    <t>23E</t>
-  </si>
-  <si>
-    <t>WESTWOOD OLYMPIA</t>
-  </si>
-  <si>
-    <t>140E</t>
   </si>
   <si>
     <t>MAERSK MAMMOTH</t>
@@ -792,10 +774,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L117" totalsRowShown="0">
-  <autoFilter ref="A1:L117" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L117">
-    <sortCondition ref="J2:J117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L111" totalsRowShown="0">
+  <autoFilter ref="A1:L111" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L111">
+    <sortCondition ref="J2:J111"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1132,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1286,12 +1268,12 @@
         <v>46325.75</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1306,62 +1288,62 @@
         <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K5" s="2">
-        <v>46321.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="1">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46320.916666666664</v>
+        <v>46321.25</v>
       </c>
       <c r="K6" s="2">
-        <v>46321.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -1376,57 +1358,57 @@
         <v>40</v>
       </c>
       <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K7" s="2">
-        <v>46322.166666666664</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" t="s">
         <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2">
-        <v>46321.25</v>
+        <v>46321.833333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46322.75</v>
+        <v>46322.770833333336</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1434,34 +1416,37 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="2">
-        <v>46321.25</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K9" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1469,34 +1454,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46321.833333333336</v>
+        <v>46322.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46322.770833333336</v>
+        <v>46325.75</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1504,37 +1489,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
         <v>58</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>60</v>
       </c>
-      <c r="H11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
       <c r="J11" s="2">
-        <v>46322.208333333336</v>
+        <v>46322.791666666664</v>
       </c>
       <c r="K11" s="2">
-        <v>46324.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1542,34 +1524,37 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J12" s="2">
-        <v>46322.625</v>
+        <v>46322.791666666664</v>
       </c>
       <c r="K12" s="2">
-        <v>46325.75</v>
+        <v>46325.770833333336</v>
       </c>
       <c r="L12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1577,72 +1562,69 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
         <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46322.791666666664</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46325.770833333336</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" s="1" t="s">
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
         <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46322.791666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K14" s="2">
         <v>46323.75</v>
       </c>
       <c r="L14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1650,69 +1632,72 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="E15" s="1">
+        <v>26173</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2">
-        <v>46323.104166666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K15" s="2">
-        <v>46323.916666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
       </c>
-      <c r="H16" t="s">
-        <v>74</v>
-      </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J16" s="2">
-        <v>46323.25</v>
+        <v>46324.25</v>
       </c>
       <c r="K16" s="2">
-        <v>46323.75</v>
+        <v>46324.833333333336</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1720,72 +1705,72 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="1">
-        <v>26173</v>
-      </c>
-      <c r="F17" t="s">
-        <v>81</v>
-      </c>
       <c r="G17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="J17" s="2">
-        <v>46323.625</v>
+        <v>46324.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46324.041666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
       </c>
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
         <v>46324.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46324.833333333336</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1793,72 +1778,69 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J19" s="2">
-        <v>46324.25</v>
+        <v>46324.875</v>
       </c>
       <c r="K19" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46324.25</v>
+        <v>46325.104166666664</v>
       </c>
       <c r="K20" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.916666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1866,34 +1848,34 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>67</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46324.875</v>
+        <v>46325.104166666664</v>
       </c>
       <c r="K21" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.916666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1901,34 +1883,31 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.208333333336</v>
       </c>
       <c r="K22" s="2">
-        <v>46326.916666666664</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1936,34 +1915,31 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.208333333336</v>
       </c>
       <c r="K23" s="2">
-        <v>46326.916666666664</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1971,31 +1947,34 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>67</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
       </c>
       <c r="J24" s="2">
-        <v>46325.208333333336</v>
+        <v>46325.291666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46326.708333333336</v>
+        <v>46326.125</v>
       </c>
       <c r="L24" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2003,66 +1982,72 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="E25" s="1">
+        <v>26172</v>
+      </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>75</v>
+      </c>
+      <c r="H25" t="s">
+        <v>75</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J25" s="2">
-        <v>46325.208333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46326.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" t="s">
         <v>96</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46325.291666666664</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K26" s="2">
-        <v>46326.125</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2070,69 +2055,69 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="1">
-        <v>26172</v>
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J27" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K27" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
+      </c>
+      <c r="L27" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="2">
-        <v>46325.958333333336</v>
+        <v>46326.625</v>
       </c>
       <c r="K28" s="2">
-        <v>46327.416666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L28" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2140,10 +2125,10 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
         <v>105</v>
@@ -2152,42 +2137,42 @@
         <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J29" s="2">
-        <v>46326.25</v>
+        <v>46327.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46326.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>108</v>
+      <c r="E30" s="1">
+        <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
@@ -2196,68 +2181,68 @@
         <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46326.625</v>
+        <v>46327.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46328.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L30" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="G31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K31" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
+        <v>114</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="G32" t="s">
         <v>18</v>
@@ -2266,59 +2251,59 @@
         <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K32" s="2">
-        <v>46331.75</v>
+        <v>46329.75</v>
       </c>
       <c r="L32" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
       </c>
+      <c r="H33" t="s">
+        <v>67</v>
+      </c>
       <c r="I33" t="s">
         <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.25</v>
       </c>
       <c r="K33" s="2">
         <v>46328.75</v>
       </c>
       <c r="L33" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
         <v>118</v>
@@ -2327,30 +2312,36 @@
         <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
       </c>
       <c r="I34" t="s">
         <v>19</v>
       </c>
       <c r="J34" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K34" s="2">
-        <v>46329.75</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>113</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -2359,25 +2350,25 @@
         <v>121</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I35" t="s">
         <v>19</v>
       </c>
       <c r="J35" s="2">
-        <v>46328.25</v>
+        <v>46329.291666666664</v>
       </c>
       <c r="K35" s="2">
-        <v>46328.75</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2385,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
         <v>122</v>
@@ -2397,63 +2388,54 @@
         <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" t="s">
-        <v>95</v>
-      </c>
-      <c r="H36" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46329.208333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.625</v>
       </c>
       <c r="L36" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
       </c>
-      <c r="H37" t="s">
-        <v>74</v>
-      </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46329.291666666664</v>
+        <v>46329.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46331.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L37" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2461,31 +2443,34 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F38" t="s">
-        <v>128</v>
+        <v>66</v>
+      </c>
+      <c r="G38" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" t="s">
+        <v>67</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.104166666664</v>
       </c>
       <c r="K38" s="2">
-        <v>46332.625</v>
+        <v>46330.916666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2493,10 +2478,10 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
         <v>129</v>
@@ -2505,22 +2490,19 @@
         <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>131</v>
-      </c>
-      <c r="G39" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46329.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46331.75</v>
+        <v>46334</v>
       </c>
       <c r="L39" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2528,34 +2510,31 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" t="s">
-        <v>73</v>
-      </c>
-      <c r="H40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
       </c>
       <c r="J40" s="2">
-        <v>46330.104166666664</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46330.916666666664</v>
+        <v>46334</v>
       </c>
       <c r="L40" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2563,31 +2542,34 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
       </c>
       <c r="I41" t="s">
         <v>19</v>
       </c>
       <c r="J41" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46334</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2595,51 +2577,48 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J42" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K42" s="2">
-        <v>46334</v>
+        <v>46331.125</v>
       </c>
       <c r="L42" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="G43" t="s">
         <v>18</v>
@@ -2648,13 +2627,13 @@
         <v>19</v>
       </c>
       <c r="J43" s="2">
-        <v>46330.25</v>
+        <v>46330.708333333336</v>
       </c>
       <c r="K43" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L43" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2662,28 +2641,34 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>135</v>
+      </c>
+      <c r="E44" s="1">
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>81</v>
+        <v>136</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J44" s="2">
-        <v>46330.625</v>
+        <v>46331.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46331.125</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2691,10 +2676,10 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
         <v>137</v>
@@ -2703,86 +2688,95 @@
         <v>138</v>
       </c>
       <c r="F45" t="s">
-        <v>128</v>
+        <v>139</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" t="s">
+        <v>140</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J45" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L45" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F46" t="s">
-        <v>128</v>
+        <v>112</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K46" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
+      </c>
+      <c r="E47" s="1">
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J47" s="2">
-        <v>46330.708333333336</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2790,83 +2784,77 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="1">
-        <v>10</v>
+        <v>137</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
       </c>
+      <c r="H48" t="s">
+        <v>140</v>
+      </c>
       <c r="I48" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J48" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K48" s="2">
-        <v>46331.666666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F49" t="s">
-        <v>144</v>
-      </c>
-      <c r="G49" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="I49" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46331.25</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K49" s="2">
-        <v>46331.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L49" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
         <v>146</v>
@@ -2875,22 +2863,22 @@
         <v>147</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46331.291666666664</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.708333333336</v>
       </c>
       <c r="L50" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2898,31 +2886,31 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" t="s">
         <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F51" t="s">
-        <v>128</v>
+        <v>51</v>
+      </c>
+      <c r="G51" t="s">
+        <v>90</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K51" s="2">
-        <v>46334.746527777781</v>
+        <v>46333.708333333336</v>
       </c>
       <c r="L51" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2930,10 +2918,10 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>148</v>
@@ -2942,54 +2930,57 @@
         <v>149</v>
       </c>
       <c r="F52" t="s">
-        <v>128</v>
+        <v>139</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J52" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L52" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
-      </c>
-      <c r="E53" s="1">
-        <v>10</v>
+        <v>150</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="G53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46331.708333333336</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K53" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2997,101 +2988,98 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F54" t="s">
-        <v>144</v>
-      </c>
-      <c r="G54" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="I54" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
-        <v>151</v>
-      </c>
-      <c r="E55" s="1" t="s">
         <v>152</v>
       </c>
       <c r="F55" t="s">
-        <v>103</v>
+        <v>66</v>
+      </c>
+      <c r="G55" t="s">
+        <v>66</v>
+      </c>
+      <c r="H55" t="s">
+        <v>67</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
       </c>
       <c r="J55" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.125</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>108</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="G56" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46333.708333333336</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3099,31 +3087,28 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>93</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
-      </c>
-      <c r="G57" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="I57" t="s">
         <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46333.708333333336</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L57" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3131,104 +3116,98 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F58" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J58" s="2">
-        <v>46332.25</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46332.75</v>
+        <v>46333.75</v>
       </c>
       <c r="L58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F59" t="s">
-        <v>116</v>
-      </c>
-      <c r="G59" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K59" s="2">
-        <v>46334.166666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="L59" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>158</v>
+      <c r="E60" s="1">
+        <v>102</v>
       </c>
       <c r="F60" t="s">
-        <v>116</v>
-      </c>
-      <c r="G60" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46332.291666666664</v>
+        <v>46333</v>
       </c>
       <c r="K60" s="2">
-        <v>46334.166666666664</v>
+        <v>46334</v>
       </c>
       <c r="L60" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3236,34 +3215,34 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>159</v>
       </c>
       <c r="F61" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J61" s="2">
-        <v>46332.291666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K61" s="2">
-        <v>46333.125</v>
+        <v>46333.75</v>
       </c>
       <c r="L61" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3271,80 +3250,98 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>72</v>
+        <v>161</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="F62" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46332.291666666664</v>
+        <v>46333.625</v>
       </c>
       <c r="K62" s="2">
-        <v>46332.791666666664</v>
+        <v>46336.166666666664</v>
       </c>
       <c r="L62" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F63" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="I63" t="s">
         <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46332.375</v>
+        <v>46333.75</v>
       </c>
       <c r="K63" s="2">
-        <v>46333.5</v>
+        <v>46335.625</v>
       </c>
       <c r="L63" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" s="1">
+        <v>11</v>
+      </c>
+      <c r="F64" t="s">
+        <v>136</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s">
+        <v>60</v>
+      </c>
+      <c r="J64" s="2">
+        <v>46334.25</v>
+      </c>
+      <c r="K64" s="2">
+        <v>46334.75</v>
+      </c>
+      <c r="L64" t="s">
         <v>36</v>
-      </c>
-      <c r="B64" t="s">
-        <v>37</v>
-      </c>
-      <c r="D64" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" t="s">
-        <v>77</v>
-      </c>
-      <c r="I64" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" s="2">
-        <v>46332.375</v>
-      </c>
-      <c r="K64" s="2">
-        <v>46333.5</v>
-      </c>
-      <c r="L64" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3352,124 +3349,127 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>166</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F65" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J65" s="2">
-        <v>46332.541666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K65" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.75</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D66" t="s">
-        <v>155</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
+      </c>
+      <c r="E66" s="1">
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>144</v>
-      </c>
-      <c r="G66" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
-        <v>46332.791666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="K66" s="2">
-        <v>46333.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L66" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" t="s">
+        <v>166</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F67" t="s">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" t="s">
+        <v>60</v>
+      </c>
+      <c r="J67" s="2">
+        <v>46334.791666666664</v>
+      </c>
+      <c r="K67" s="2">
+        <v>46335.75</v>
+      </c>
+      <c r="L67" t="s">
         <v>36</v>
-      </c>
-      <c r="B67" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" t="s">
-        <v>161</v>
-      </c>
-      <c r="D67" t="s">
-        <v>162</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F67" t="s">
-        <v>164</v>
-      </c>
-      <c r="I67" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" s="2">
-        <v>46332.875</v>
-      </c>
-      <c r="K67" s="2">
-        <v>46334.25</v>
-      </c>
-      <c r="L67" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
-      </c>
-      <c r="E68" s="1">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="F68" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
       </c>
       <c r="J68" s="2">
-        <v>46333</v>
+        <v>46335.1875</v>
       </c>
       <c r="K68" s="2">
-        <v>46334</v>
+        <v>46336.3125</v>
       </c>
       <c r="L68" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3477,66 +3477,69 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>166</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="G69" t="s">
         <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J69" s="2">
-        <v>46333.25</v>
+        <v>46335.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46333.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" t="s">
+        <v>170</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" t="s">
+        <v>60</v>
+      </c>
+      <c r="J70" s="2">
+        <v>46335.791666666664</v>
+      </c>
+      <c r="K70" s="2">
+        <v>46336.75</v>
+      </c>
+      <c r="L70" t="s">
         <v>36</v>
-      </c>
-      <c r="B70" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" t="s">
-        <v>43</v>
-      </c>
-      <c r="D70" t="s">
-        <v>169</v>
-      </c>
-      <c r="E70" s="1">
-        <v>94</v>
-      </c>
-      <c r="F70" t="s">
-        <v>46</v>
-      </c>
-      <c r="I70" t="s">
-        <v>19</v>
-      </c>
-      <c r="J70" s="2">
-        <v>46333.666666666664</v>
-      </c>
-      <c r="K70" s="2">
-        <v>46335.041666666664</v>
-      </c>
-      <c r="L70" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3544,34 +3547,31 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>86</v>
-      </c>
-      <c r="G71" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I71" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46334.25</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46334.75</v>
+        <v>46338.125</v>
       </c>
       <c r="L71" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3579,69 +3579,63 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
-      </c>
-      <c r="E72" s="1">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="F72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G72" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I72" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46334.25</v>
+        <v>46337</v>
       </c>
       <c r="K72" s="2">
-        <v>46334.75</v>
+        <v>46339</v>
       </c>
       <c r="L72" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F73" t="s">
-        <v>86</v>
-      </c>
-      <c r="G73" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="I73" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46334.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46335.75</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L73" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3649,31 +3643,28 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D74" t="s">
-        <v>173</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="F74" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46334.958333333336</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46337.708333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L74" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3681,34 +3672,28 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
-      </c>
-      <c r="E75" s="1">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="F75" t="s">
-        <v>33</v>
-      </c>
-      <c r="G75" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I75" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="J75" s="2">
-        <v>46335.25</v>
+        <v>46337.625</v>
       </c>
       <c r="K75" s="2">
-        <v>46335.75</v>
+        <v>46338.125</v>
       </c>
       <c r="L75" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3716,156 +3701,159 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>175</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F76" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J76" s="2">
-        <v>46335.791666666664</v>
+        <v>46338.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46336.75</v>
+        <v>46338.75</v>
       </c>
       <c r="L76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F77" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46337</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K77" s="2">
-        <v>46339</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L77" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>180</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="F78" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K78" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L78" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
+      </c>
+      <c r="E79" s="1">
+        <v>145</v>
       </c>
       <c r="F79" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46337.333333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46339.333333333336</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L79" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
+        <v>182</v>
+      </c>
+      <c r="E80" s="1">
+        <v>145</v>
       </c>
       <c r="F80" t="s">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="I80" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46337.625</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46338.125</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L80" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3873,95 +3861,86 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="F81" t="s">
-        <v>86</v>
-      </c>
-      <c r="G81" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I81" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46338.25</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46338.75</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L81" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46338.431250000001</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K82" s="2">
-        <v>46339.472916666666</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L82" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C83" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
-        <v>183</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="F83" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46338.709027777775</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.75</v>
       </c>
       <c r="L83" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3969,16 +3948,16 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D84" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -3987,13 +3966,13 @@
         <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46338.958333333336</v>
+        <v>46341.208333333336</v>
       </c>
       <c r="K84" s="2">
-        <v>46342.208333333336</v>
+        <v>46343.708333333336</v>
       </c>
       <c r="L84" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4001,127 +3980,133 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>139</v>
+      </c>
+      <c r="G85" t="s">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s">
+        <v>188</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J85" s="2">
-        <v>46338.958333333336</v>
+        <v>46341.25</v>
       </c>
       <c r="K85" s="2">
-        <v>46342.208333333336</v>
+        <v>46341.75</v>
       </c>
       <c r="L85" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="D86" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46339.083333333336</v>
+        <v>46341.333333333336</v>
       </c>
       <c r="K86" s="2">
-        <v>46340.291666666664</v>
+        <v>46342.333333333336</v>
       </c>
       <c r="L86" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E87" s="1">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="F87" t="s">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46339.291666666664</v>
+        <v>46341.62777777778</v>
       </c>
       <c r="K87" s="2">
-        <v>46340.666666666664</v>
+        <v>46346.00277777778</v>
       </c>
       <c r="L87" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" t="s">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" t="s">
+        <v>60</v>
+      </c>
+      <c r="J88" s="2">
+        <v>46342.25</v>
+      </c>
+      <c r="K88" s="2">
+        <v>46342.75</v>
+      </c>
+      <c r="L88" t="s">
         <v>36</v>
-      </c>
-      <c r="B88" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" t="s">
-        <v>161</v>
-      </c>
-      <c r="D88" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="1">
-        <v>145</v>
-      </c>
-      <c r="F88" t="s">
-        <v>164</v>
-      </c>
-      <c r="I88" t="s">
-        <v>19</v>
-      </c>
-      <c r="J88" s="2">
-        <v>46339.291666666664</v>
-      </c>
-      <c r="K88" s="2">
-        <v>46340.666666666664</v>
-      </c>
-      <c r="L88" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4129,25 +4114,28 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>193</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
       </c>
       <c r="J89" s="2">
-        <v>46339.541666666664</v>
+        <v>46342.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46340.041666666664</v>
+        <v>46344.25</v>
+      </c>
+      <c r="L89" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4155,28 +4143,34 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C90" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F90" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J90" s="2">
-        <v>46339.704861111109</v>
+        <v>46342.791666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46340.204861111109</v>
+        <v>46343.75</v>
       </c>
       <c r="L90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4184,28 +4178,31 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>195</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F91" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="I91" t="s">
         <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46340.416666666664</v>
+        <v>46343.208333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46340.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L91" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4213,98 +4210,104 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C92" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F92" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s">
         <v>18</v>
       </c>
       <c r="H92" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="I92" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J92" s="2">
-        <v>46341.25</v>
+        <v>46343.25</v>
       </c>
       <c r="K92" s="2">
-        <v>46341.75</v>
+        <v>46343.75</v>
       </c>
       <c r="L92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" t="s">
+        <v>32</v>
+      </c>
+      <c r="D93" t="s">
+        <v>199</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F93" t="s">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s">
+        <v>60</v>
+      </c>
+      <c r="J93" s="2">
+        <v>46343.25</v>
+      </c>
+      <c r="K93" s="2">
+        <v>46343.75</v>
+      </c>
+      <c r="L93" t="s">
         <v>36</v>
-      </c>
-      <c r="B93" t="s">
-        <v>112</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
-        <v>194</v>
-      </c>
-      <c r="F93" t="s">
-        <v>116</v>
-      </c>
-      <c r="I93" t="s">
-        <v>19</v>
-      </c>
-      <c r="J93" s="2">
-        <v>46341.333333333336</v>
-      </c>
-      <c r="K93" s="2">
-        <v>46342.333333333336</v>
-      </c>
-      <c r="L93" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>195</v>
-      </c>
-      <c r="E94" s="1">
-        <v>57</v>
+        <v>201</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F94" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
       </c>
       <c r="J94" s="2">
-        <v>46341.62777777778</v>
+        <v>46343.3125</v>
       </c>
       <c r="K94" s="2">
-        <v>46346.00277777778</v>
+        <v>46346.604166666664</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4312,31 +4315,34 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D95" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F95" t="s">
-        <v>128</v>
+        <v>80</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J95" s="2">
-        <v>46342.1875</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46345.770833333336</v>
+        <v>46344.75</v>
       </c>
       <c r="L95" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4344,63 +4350,57 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D96" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F96" t="s">
-        <v>86</v>
-      </c>
-      <c r="G96" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I96" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46342.25</v>
+        <v>46344</v>
       </c>
       <c r="K96" s="2">
-        <v>46342.75</v>
+        <v>46346</v>
       </c>
       <c r="L96" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>200</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46342.25</v>
+        <v>46344.083333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46344.25</v>
+        <v>46345.208333333336</v>
       </c>
       <c r="L97" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4408,34 +4408,28 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D98" t="s">
-        <v>198</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="F98" t="s">
-        <v>86</v>
-      </c>
-      <c r="G98" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I98" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46342.791666666664</v>
+        <v>46344.291666666664</v>
       </c>
       <c r="K98" s="2">
-        <v>46343.75</v>
+        <v>46344.791666666664</v>
       </c>
       <c r="L98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4443,37 +4437,28 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="F99" t="s">
-        <v>86</v>
-      </c>
-      <c r="G99" t="s">
-        <v>18</v>
-      </c>
-      <c r="H99" t="s">
         <v>74</v>
       </c>
       <c r="I99" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="J99" s="2">
-        <v>46343.25</v>
+        <v>46344.625</v>
       </c>
       <c r="K99" s="2">
-        <v>46343.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L99" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4481,34 +4466,34 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J100" s="2">
-        <v>46343.25</v>
+        <v>46345.25</v>
       </c>
       <c r="K100" s="2">
-        <v>46343.75</v>
+        <v>46345.75</v>
       </c>
       <c r="L100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4516,63 +4501,69 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="E101" s="1">
+        <v>89</v>
       </c>
       <c r="F101" t="s">
-        <v>208</v>
+        <v>136</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" t="s">
+        <v>210</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J101" s="2">
-        <v>46343.3125</v>
+        <v>46345.25</v>
       </c>
       <c r="K101" s="2">
-        <v>46346.604166666664</v>
+        <v>46345.75</v>
       </c>
       <c r="L101" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F102" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
       </c>
       <c r="J102" s="2">
-        <v>46343.333333333336</v>
+        <v>46345.291666666664</v>
       </c>
       <c r="K102" s="2">
         <v>46346.166666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4580,34 +4571,31 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D103" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F103" t="s">
-        <v>86</v>
-      </c>
-      <c r="G103" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I103" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J103" s="2">
-        <v>46343.791666666664</v>
+        <v>46345.395833333336</v>
       </c>
       <c r="K103" s="2">
-        <v>46344.75</v>
+        <v>46349.1875</v>
       </c>
       <c r="L103" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4615,63 +4603,63 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F104" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
       </c>
       <c r="J104" s="2">
-        <v>46344</v>
+        <v>46345.395833333336</v>
       </c>
       <c r="K104" s="2">
-        <v>46346</v>
+        <v>46349.1875</v>
       </c>
       <c r="L104" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D105" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F105" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
       </c>
       <c r="J105" s="2">
-        <v>46344.208333333336</v>
+        <v>46346.23333333333</v>
       </c>
       <c r="K105" s="2">
-        <v>46347.208333333336</v>
+        <v>46347.275000000001</v>
       </c>
       <c r="L105" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4679,95 +4667,92 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C106" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D106" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F106" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
       </c>
       <c r="J106" s="2">
-        <v>46344.291666666664</v>
+        <v>46346.333333333336</v>
       </c>
       <c r="K106" s="2">
-        <v>46344.791666666664</v>
+        <v>46346.833333333336</v>
       </c>
       <c r="L106" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="D107" t="s">
-        <v>80</v>
+        <v>217</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="F107" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I107" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="J107" s="2">
-        <v>46344.625</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K107" s="2">
-        <v>46345.125</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L107" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>215</v>
-      </c>
-      <c r="E108" s="1">
-        <v>89</v>
+        <v>217</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
-      </c>
-      <c r="G108" t="s">
-        <v>18</v>
-      </c>
-      <c r="H108" t="s">
-        <v>216</v>
+        <v>124</v>
       </c>
       <c r="I108" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J108" s="2">
-        <v>46345.25</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K108" s="2">
-        <v>46345.75</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L108" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4775,45 +4760,39 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="D109" t="s">
-        <v>217</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="F109" t="s">
-        <v>86</v>
-      </c>
-      <c r="G109" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I109" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J109" s="2">
-        <v>46345.25</v>
+        <v>46346.541666666664</v>
       </c>
       <c r="K109" s="2">
-        <v>46345.75</v>
+        <v>46347.041666666664</v>
       </c>
       <c r="L109" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D110" t="s">
         <v>219</v>
@@ -4822,234 +4801,51 @@
         <v>220</v>
       </c>
       <c r="F110" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
       </c>
       <c r="J110" s="2">
-        <v>46345.291666666664</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K110" s="2">
-        <v>46346.166666666664</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L110" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D111" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
       </c>
       <c r="J111" s="2">
-        <v>46345.395833333336</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K111" s="2">
-        <v>46349.1875</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L111" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12">
-      <c r="A112" t="s">
-        <v>12</v>
-      </c>
-      <c r="B112" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" t="s">
-        <v>221</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F112" t="s">
-        <v>23</v>
-      </c>
-      <c r="I112" t="s">
-        <v>19</v>
-      </c>
-      <c r="J112" s="2">
-        <v>46345.395833333336</v>
-      </c>
-      <c r="K112" s="2">
-        <v>46349.1875</v>
-      </c>
-      <c r="L112" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
-      <c r="A113" t="s">
-        <v>36</v>
-      </c>
-      <c r="B113" t="s">
-        <v>37</v>
-      </c>
-      <c r="C113" t="s">
-        <v>150</v>
-      </c>
-      <c r="D113" t="s">
-        <v>223</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F113" t="s">
-        <v>103</v>
-      </c>
-      <c r="I113" t="s">
-        <v>19</v>
-      </c>
-      <c r="J113" s="2">
-        <v>46346.23333333333</v>
-      </c>
-      <c r="K113" s="2">
-        <v>46347.275000000001</v>
-      </c>
-      <c r="L113" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" t="s">
-        <v>70</v>
-      </c>
-      <c r="C114" t="s">
-        <v>71</v>
-      </c>
-      <c r="D114" t="s">
-        <v>92</v>
-      </c>
-      <c r="F114" t="s">
-        <v>73</v>
-      </c>
-      <c r="I114" t="s">
-        <v>19</v>
-      </c>
-      <c r="J114" s="2">
-        <v>46346.333333333336</v>
-      </c>
-      <c r="K114" s="2">
-        <v>46346.833333333336</v>
-      </c>
-      <c r="L114" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
-      <c r="A115" t="s">
-        <v>12</v>
-      </c>
-      <c r="B115" t="s">
-        <v>78</v>
-      </c>
-      <c r="C115" t="s">
-        <v>98</v>
-      </c>
-      <c r="D115" t="s">
-        <v>99</v>
-      </c>
-      <c r="F115" t="s">
-        <v>81</v>
-      </c>
-      <c r="I115" t="s">
-        <v>19</v>
-      </c>
-      <c r="J115" s="2">
-        <v>46346.541666666664</v>
-      </c>
-      <c r="K115" s="2">
-        <v>46347.041666666664</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12">
-      <c r="A116" t="s">
-        <v>36</v>
-      </c>
-      <c r="B116" t="s">
-        <v>37</v>
-      </c>
-      <c r="C116" t="s">
-        <v>89</v>
-      </c>
-      <c r="D116" t="s">
-        <v>225</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F116" t="s">
-        <v>208</v>
-      </c>
-      <c r="I116" t="s">
-        <v>19</v>
-      </c>
-      <c r="J116" s="2">
-        <v>46346.583333333336</v>
-      </c>
-      <c r="K116" s="2">
-        <v>46348.083333333336</v>
-      </c>
-      <c r="L116" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
-      <c r="A117" t="s">
-        <v>36</v>
-      </c>
-      <c r="B117" t="s">
-        <v>37</v>
-      </c>
-      <c r="C117" t="s">
-        <v>89</v>
-      </c>
-      <c r="D117" t="s">
-        <v>225</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F117" t="s">
-        <v>208</v>
-      </c>
-      <c r="I117" t="s">
-        <v>19</v>
-      </c>
-      <c r="J117" s="2">
-        <v>46346.583333333336</v>
-      </c>
-      <c r="K117" s="2">
-        <v>46348.083333333336</v>
-      </c>
-      <c r="L117" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5061,6 +4857,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5198,41 +5011,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-26.xlsx
+++ b/data/vessels/2026-10-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="459096" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1AFFF46-4A26-4E64-B6ED-A44E5BA6024D}"/>
+  <xr:revisionPtr revIDLastSave="460296" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{927BBED8-F79D-46B5-82B6-4DAFA2469EF4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="216">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,493 +83,478 @@
     <t>Husky</t>
   </si>
   <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>At berth</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>198E</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>RED CLOUD</t>
+  </si>
+  <si>
+    <t>KRF</t>
+  </si>
+  <si>
+    <t>833rd Trans Bn Sddc</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>129W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>ACGI</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
   </si>
   <si>
     <t>Hapag-Lloyd</t>
   </si>
   <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>At berth</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>010W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>015E/016W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CYPRESS</t>
+  </si>
+  <si>
+    <t>CPN06/CPN07</t>
+  </si>
+  <si>
+    <t>EUROPEAN HIGHWAY</t>
+  </si>
+  <si>
+    <t>285A</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
+    <t>SM TIANJIN</t>
+  </si>
+  <si>
+    <t>2606E/2606W</t>
+  </si>
+  <si>
+    <t>EVER SMILE</t>
+  </si>
+  <si>
+    <t>136W</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK642R</t>
+  </si>
+  <si>
+    <t>HYUNDAI FORWARD</t>
+  </si>
+  <si>
+    <t>PN32640W</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>ONE FANTASTIC</t>
+  </si>
+  <si>
+    <t>FP22633C</t>
+  </si>
+  <si>
+    <t>ONE MAJESTY</t>
+  </si>
+  <si>
+    <t>26E</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD COLUMBIA</t>
+  </si>
+  <si>
+    <t>156E</t>
+  </si>
+  <si>
+    <t>EVER MOST</t>
+  </si>
+  <si>
+    <t>011W</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>MSC YUKTA X</t>
+  </si>
+  <si>
+    <t>UK644R</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SEATTLE</t>
+  </si>
+  <si>
+    <t>46E</t>
+  </si>
+  <si>
+    <t>OOCL</t>
   </si>
   <si>
     <t>CPV</t>
   </si>
   <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
+    <t>COSCO SANTOS</t>
   </si>
   <si>
     <t>COSCO</t>
   </si>
   <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>198E</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>RED CLOUD</t>
-  </si>
-  <si>
-    <t>KRF</t>
-  </si>
-  <si>
-    <t>833rd Trans Bn Sddc</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>129W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>ACGI</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>010W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>015E/016W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CYPRESS</t>
-  </si>
-  <si>
-    <t>CPN06/CPN07</t>
-  </si>
-  <si>
-    <t>EUROPEAN HIGHWAY</t>
-  </si>
-  <si>
-    <t>285A</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>SM TIANJIN</t>
-  </si>
-  <si>
-    <t>2606E/2606W</t>
-  </si>
-  <si>
-    <t>EVER SMILE</t>
-  </si>
-  <si>
-    <t>136W</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK642R</t>
+    <t>NOCC ADRIATIC</t>
+  </si>
+  <si>
+    <t>KW667</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>CORNEILLE</t>
+  </si>
+  <si>
+    <t>14E</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>BUDAPEST EXPRESS</t>
+  </si>
+  <si>
+    <t>641E</t>
+  </si>
+  <si>
+    <t>SWIFT ACE</t>
+  </si>
+  <si>
+    <t>152A</t>
+  </si>
+  <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
+    <t>LOTUS A</t>
+  </si>
+  <si>
+    <t>SM MUMBAI</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
+    <t>ONE MODERN</t>
+  </si>
+  <si>
+    <t>83E</t>
+  </si>
+  <si>
+    <t>EVER STRONG</t>
+  </si>
+  <si>
+    <t>497-134E</t>
+  </si>
+  <si>
+    <t>MSC LISBON IX</t>
+  </si>
+  <si>
+    <t>UK641A</t>
   </si>
   <si>
     <t>SANTA RITA</t>
   </si>
   <si>
-    <t>642E</t>
-  </si>
-  <si>
-    <t>Not Specified</t>
-  </si>
-  <si>
-    <t>HYUNDAI FORWARD</t>
-  </si>
-  <si>
-    <t>PN32640W</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>ONE FANTASTIC</t>
-  </si>
-  <si>
-    <t>FP22633C</t>
-  </si>
-  <si>
-    <t>ONE MAJESTY</t>
-  </si>
-  <si>
-    <t>26E</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC644R</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC645R</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD COLUMBIA</t>
-  </si>
-  <si>
-    <t>156E</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>011W</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
-    <t>MSC YUKTA X</t>
-  </si>
-  <si>
-    <t>UK644R</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SEATTLE</t>
-  </si>
-  <si>
-    <t>46E</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>COSCO SANTOS</t>
-  </si>
-  <si>
-    <t>NOCC ADRIATIC</t>
-  </si>
-  <si>
-    <t>KW667</t>
-  </si>
-  <si>
-    <t>Eukor</t>
-  </si>
-  <si>
-    <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>BUDAPEST EXPRESS</t>
-  </si>
-  <si>
-    <t>641E</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
-  </si>
-  <si>
-    <t>SWIFT ACE</t>
-  </si>
-  <si>
-    <t>152A</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>SM MUMBAI</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>ONE MODERN</t>
-  </si>
-  <si>
-    <t>83E</t>
-  </si>
-  <si>
-    <t>EVER STRONG</t>
-  </si>
-  <si>
-    <t>497-134E</t>
-  </si>
-  <si>
-    <t>MSC LISBON IX</t>
-  </si>
-  <si>
-    <t>UK641A</t>
+    <t>651E</t>
   </si>
   <si>
     <t>SUPREME ACE</t>
@@ -632,16 +617,16 @@
     <t>308E</t>
   </si>
   <si>
+    <t>TOURMALINE ACE</t>
+  </si>
+  <si>
+    <t>013A</t>
+  </si>
+  <si>
     <t>EUPHONY ACE</t>
   </si>
   <si>
     <t>166A</t>
-  </si>
-  <si>
-    <t>TOURMALINE ACE</t>
-  </si>
-  <si>
-    <t>013A</t>
   </si>
   <si>
     <t>MAERSK SARNIA</t>
@@ -774,10 +759,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L111" totalsRowShown="0">
-  <autoFilter ref="A1:L111" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L111">
-    <sortCondition ref="J2:J111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L110" totalsRowShown="0">
+  <autoFilter ref="A1:L110" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L110">
+    <sortCondition ref="J2:J110"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1114,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1179,61 +1164,61 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="1">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2">
+        <v>46319.25</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46325.75</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
-      </c>
-      <c r="J2" s="2">
-        <v>46315.916666666664</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46322.166666666664</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2">
-        <v>46315.916666666664</v>
+        <v>46321.25</v>
       </c>
       <c r="K3" s="2">
-        <v>46322.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1241,104 +1226,107 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="1">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2">
+        <v>46321.25</v>
+      </c>
+      <c r="K4" s="2">
+        <v>46323.166666666664</v>
+      </c>
+      <c r="L4" t="s">
         <v>19</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46319.25</v>
-      </c>
-      <c r="K4" s="2">
-        <v>46325.75</v>
-      </c>
-      <c r="L4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="2">
+        <v>46321.833333333336</v>
+      </c>
+      <c r="K5" s="2">
+        <v>46322.770833333336</v>
+      </c>
+      <c r="L5" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="2">
-        <v>46321.208333333336</v>
-      </c>
-      <c r="K5" s="2">
-        <v>46322.166666666664</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2">
-        <v>46321.25</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46322.75</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1346,34 +1334,34 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2">
-        <v>46321.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K7" s="2">
-        <v>46323.166666666664</v>
+        <v>46329.75</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1381,34 +1369,34 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J8" s="2">
-        <v>46321.833333333336</v>
+        <v>46322.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46322.770833333336</v>
+        <v>46329.75</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1416,37 +1404,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
       </c>
       <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>53</v>
       </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
       <c r="J9" s="2">
-        <v>46322.208333333336</v>
+        <v>46322.791666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46324.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1454,10 +1439,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>54</v>
@@ -1466,22 +1451,25 @@
         <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J10" s="2">
-        <v>46322.625</v>
+        <v>46322.791666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46325.75</v>
+        <v>46325.770833333336</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1492,42 +1480,39 @@
         <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46322.791666666664</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K11" s="2">
-        <v>46323.75</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>61</v>
@@ -1536,25 +1521,25 @@
         <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46322.791666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K12" s="2">
-        <v>46325.770833333336</v>
+        <v>46323.75</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1562,69 +1547,72 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E13" s="1">
+        <v>26173</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J13" s="2">
-        <v>46323.104166666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K13" s="2">
-        <v>46323.916666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J14" s="2">
-        <v>46323.25</v>
+        <v>46324.25</v>
       </c>
       <c r="K14" s="2">
-        <v>46323.75</v>
+        <v>46324.833333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1632,48 +1620,45 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="1">
-        <v>26173</v>
-      </c>
-      <c r="F15" t="s">
-        <v>74</v>
-      </c>
       <c r="G15" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46323.625</v>
+        <v>46324.25</v>
       </c>
       <c r="K15" s="2">
-        <v>46324.041666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>78</v>
@@ -1682,22 +1667,25 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2">
         <v>46324.25</v>
       </c>
       <c r="K16" s="2">
-        <v>46324.833333333336</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1705,72 +1693,69 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J17" s="2">
-        <v>46324.25</v>
+        <v>46324.875</v>
       </c>
       <c r="K17" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" s="2">
-        <v>46324.25</v>
+        <v>46325.104166666664</v>
       </c>
       <c r="K18" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.916666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1781,31 +1766,31 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="H19" t="s">
+        <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46324.875</v>
+        <v>46325.104166666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.916666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1813,34 +1798,31 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.208333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46326.916666666664</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1848,34 +1830,31 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" s="2">
-        <v>46325.104166666664</v>
+        <v>46325.208333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46326.916666666664</v>
+        <v>46326.708333333336</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1883,31 +1862,34 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>59</v>
+      </c>
+      <c r="H22" t="s">
+        <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46325.208333333336</v>
+        <v>46325.291666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46326.708333333336</v>
+        <v>46326.125</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1915,66 +1897,72 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="E23" s="1">
+        <v>26172</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>68</v>
+      </c>
+      <c r="H23" t="s">
+        <v>68</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J23" s="2">
-        <v>46325.208333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K23" s="2">
-        <v>46326.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
         <v>91</v>
       </c>
-      <c r="D24" t="s">
+      <c r="G24" t="s">
         <v>92</v>
       </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" t="s">
-        <v>67</v>
-      </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46325.291666666664</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46326.125</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1982,45 +1970,42 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
         <v>93</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="1">
-        <v>26172</v>
-      </c>
       <c r="F25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J25" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L25" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
         <v>95</v>
@@ -2032,22 +2017,22 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46325.958333333336</v>
+        <v>46326.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46327.416666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L26" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2055,244 +2040,250 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J27" s="2">
-        <v>46326.25</v>
+        <v>46327.25</v>
       </c>
       <c r="K27" s="2">
-        <v>46326.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L27" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46326.625</v>
+        <v>46327.625</v>
       </c>
       <c r="K28" s="2">
-        <v>46328.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L28" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" t="s">
-        <v>80</v>
-      </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K29" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.75</v>
       </c>
       <c r="L29" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="1">
-        <v>2</v>
+      <c r="E30" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46331.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L30" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
         <v>109</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H31" t="s">
+        <v>60</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.25</v>
       </c>
       <c r="K31" s="2">
         <v>46328.75</v>
       </c>
       <c r="L31" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>83</v>
+      </c>
+      <c r="H32" t="s">
+        <v>43</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K32" s="2">
-        <v>46329.75</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>101</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2">
-        <v>46328.25</v>
+        <v>46329.291666666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46328.75</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2300,75 +2291,69 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46329.208333333336</v>
+        <v>46329.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L34" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="H35" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35" s="2">
-        <v>46329.291666666664</v>
+        <v>46330.104166666664</v>
       </c>
       <c r="K35" s="2">
-        <v>46331.166666666664</v>
+        <v>46330.916666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2382,25 +2367,25 @@
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F36" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L36" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2408,34 +2393,31 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G37" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J37" s="2">
-        <v>46329.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K37" s="2">
-        <v>46331.75</v>
+        <v>46334</v>
       </c>
       <c r="L37" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2443,34 +2425,34 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>121</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
-      </c>
-      <c r="H38" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46330.104166666664</v>
+        <v>46330.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46330.916666666664</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2478,63 +2460,63 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J39" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K39" s="2">
-        <v>46334</v>
+        <v>46331.125</v>
       </c>
       <c r="L39" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
+        <v>105</v>
+      </c>
+      <c r="G40" t="s">
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.708333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46334</v>
+        <v>46331.75</v>
       </c>
       <c r="L40" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2542,34 +2524,34 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J41" s="2">
-        <v>46330.25</v>
+        <v>46331.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2577,63 +2559,72 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>127</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>129</v>
+      </c>
+      <c r="G42" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" t="s">
+        <v>130</v>
       </c>
       <c r="I42" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J42" s="2">
-        <v>46330.625</v>
+        <v>46331.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46331.125</v>
+        <v>46331.75</v>
       </c>
       <c r="L42" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F43" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46330.708333333336</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2641,34 +2632,34 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E44" s="1">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J44" s="2">
-        <v>46331.25</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K44" s="2">
-        <v>46331.666666666664</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2676,72 +2667,69 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I45" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J45" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K45" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L45" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
-      </c>
-      <c r="G46" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46331.291666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K46" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L46" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2749,34 +2737,31 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="1">
-        <v>10</v>
+        <v>136</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46331.708333333336</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.708333333336</v>
       </c>
       <c r="L47" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2784,101 +2769,101 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.208333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46332.75</v>
+        <v>46333.708333333336</v>
       </c>
       <c r="L48" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>129</v>
+      </c>
+      <c r="G49" t="s">
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J49" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>101</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46333.708333333336</v>
+        <v>46334.166666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2886,31 +2871,28 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="C51" t="s">
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
-      </c>
-      <c r="G51" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46332.208333333336</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K51" s="2">
-        <v>46333.708333333336</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2918,60 +2900,60 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F52" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="H52" t="s">
+        <v>60</v>
       </c>
       <c r="I52" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K52" s="2">
-        <v>46332.75</v>
+        <v>46333.125</v>
       </c>
       <c r="L52" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F53" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J53" s="2">
         <v>46332.291666666664</v>
@@ -2980,7 +2962,7 @@
         <v>46334.166666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2988,28 +2970,28 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="F54" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3017,98 +2999,98 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>138</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="F55" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="G55" t="s">
-        <v>66</v>
-      </c>
-      <c r="H55" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J55" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46333.125</v>
+        <v>46333.75</v>
       </c>
       <c r="L55" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
-      </c>
-      <c r="G56" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K56" s="2">
-        <v>46334.166666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="L56" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="D57" t="s">
-        <v>94</v>
+        <v>148</v>
+      </c>
+      <c r="E57" s="1">
+        <v>102</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46332.541666666664</v>
+        <v>46333</v>
       </c>
       <c r="K57" s="2">
-        <v>46333.041666666664</v>
+        <v>46334</v>
       </c>
       <c r="L57" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3116,98 +3098,98 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F58" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J58" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K58" s="2">
         <v>46333.75</v>
       </c>
       <c r="L58" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s">
         <v>153</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" t="s">
         <v>155</v>
       </c>
-      <c r="F59" t="s">
-        <v>156</v>
-      </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46332.875</v>
+        <v>46333.625</v>
       </c>
       <c r="K59" s="2">
-        <v>46334.25</v>
+        <v>46336.166666666664</v>
       </c>
       <c r="L59" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="1">
-        <v>102</v>
-      </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46333</v>
+        <v>46333.75</v>
       </c>
       <c r="K60" s="2">
-        <v>46334</v>
+        <v>46335.625</v>
       </c>
       <c r="L60" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3215,10 +3197,10 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
         <v>158</v>
@@ -3227,22 +3209,22 @@
         <v>159</v>
       </c>
       <c r="F61" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J61" s="2">
-        <v>46333.25</v>
+        <v>46334.25</v>
       </c>
       <c r="K61" s="2">
-        <v>46333.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L61" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3250,63 +3232,66 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>161</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
+      </c>
+      <c r="E62" s="1">
+        <v>11</v>
       </c>
       <c r="F62" t="s">
-        <v>124</v>
+        <v>126</v>
+      </c>
+      <c r="G62" t="s">
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J62" s="2">
-        <v>46333.625</v>
+        <v>46334.25</v>
       </c>
       <c r="K62" s="2">
-        <v>46336.166666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L62" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>163</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
+      </c>
+      <c r="E63" s="1">
+        <v>94</v>
       </c>
       <c r="F63" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46333.75</v>
+        <v>46334.75</v>
       </c>
       <c r="K63" s="2">
-        <v>46335.625</v>
+        <v>46337.75</v>
       </c>
       <c r="L63" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3314,101 +3299,95 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>165</v>
-      </c>
-      <c r="E64" s="1">
-        <v>11</v>
+        <v>158</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F64" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J64" s="2">
-        <v>46334.25</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K64" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L64" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>166</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F65" t="s">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46334.25</v>
+        <v>46335.1875</v>
       </c>
       <c r="K65" s="2">
-        <v>46334.75</v>
+        <v>46336.3125</v>
       </c>
       <c r="L65" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E66" s="1">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="G66" t="s">
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J66" s="2">
-        <v>46334.75</v>
+        <v>46335.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46337.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L66" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3416,60 +3395,66 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>166</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J67" s="2">
-        <v>46334.791666666664</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46335.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L67" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>74</v>
       </c>
       <c r="D68" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46335.1875</v>
+        <v>46336.208333333336</v>
       </c>
       <c r="K68" s="2">
-        <v>46336.3125</v>
+        <v>46338.125</v>
       </c>
       <c r="L68" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3477,69 +3462,63 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
+        <v>166</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F69" t="s">
-        <v>136</v>
-      </c>
-      <c r="G69" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I69" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46335.25</v>
+        <v>46337</v>
       </c>
       <c r="K69" s="2">
-        <v>46335.75</v>
+        <v>46339</v>
       </c>
       <c r="L69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F70" t="s">
-        <v>136</v>
-      </c>
-      <c r="G70" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="I70" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46335.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K70" s="2">
-        <v>46336.75</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L70" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3547,31 +3526,28 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="F71" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46336.208333333336</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46338.125</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L71" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3579,63 +3555,60 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C72" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="F72" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J72" s="2">
-        <v>46337</v>
+        <v>46337.625</v>
       </c>
       <c r="K72" s="2">
-        <v>46339</v>
+        <v>46338.125</v>
       </c>
       <c r="L72" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F73" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K73" s="2">
-        <v>46339.333333333336</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L73" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3643,28 +3616,31 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>87</v>
+        <v>170</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F74" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.913888888892</v>
       </c>
       <c r="K74" s="2">
-        <v>46337.833333333336</v>
+        <v>46341.205555555556</v>
       </c>
       <c r="L74" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3672,147 +3648,150 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
+        <v>172</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F75" t="s">
         <v>73</v>
       </c>
-      <c r="F75" t="s">
-        <v>74</v>
+      <c r="G75" t="s">
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J75" s="2">
-        <v>46337.625</v>
+        <v>46338.25</v>
       </c>
       <c r="K75" s="2">
-        <v>46338.125</v>
+        <v>46338.75</v>
       </c>
       <c r="L75" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J76" s="2">
-        <v>46338.25</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K76" s="2">
-        <v>46338.75</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L76" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>175</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="F77" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K77" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L77" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
+      </c>
+      <c r="E78" s="1">
+        <v>145</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L78" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1">
         <v>145</v>
       </c>
       <c r="F79" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J79" s="2">
         <v>46339.291666666664</v>
@@ -3821,39 +3800,36 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L79" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C80" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
-      </c>
-      <c r="E80" s="1">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L80" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3861,28 +3837,28 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D81" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46339.541666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K81" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L81" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3890,28 +3866,28 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D82" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46339.704861111109</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46340.204861111109</v>
+        <v>46340.75</v>
       </c>
       <c r="L82" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3919,28 +3895,31 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>179</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F83" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46340.416666666664</v>
+        <v>46341.208333333336</v>
       </c>
       <c r="K83" s="2">
-        <v>46340.75</v>
+        <v>46343.708333333336</v>
       </c>
       <c r="L83" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3948,130 +3927,133 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C84" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>129</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" t="s">
+        <v>183</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J84" s="2">
-        <v>46341.208333333336</v>
+        <v>46341.25</v>
       </c>
       <c r="K84" s="2">
-        <v>46343.708333333336</v>
+        <v>46341.75</v>
       </c>
       <c r="L84" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F85" t="s">
-        <v>139</v>
-      </c>
-      <c r="G85" t="s">
-        <v>18</v>
-      </c>
-      <c r="H85" t="s">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="I85" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46341.25</v>
+        <v>46341.333333333336</v>
       </c>
       <c r="K85" s="2">
-        <v>46341.75</v>
+        <v>46342.333333333336</v>
       </c>
       <c r="L85" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D86" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="E86" s="1">
+        <v>57</v>
       </c>
       <c r="F86" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J86" s="2">
-        <v>46341.333333333336</v>
+        <v>46341.62777777778</v>
       </c>
       <c r="K86" s="2">
-        <v>46342.333333333336</v>
+        <v>46346.00277777778</v>
       </c>
       <c r="L86" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="D87" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" s="1">
-        <v>57</v>
+        <v>186</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="F87" t="s">
-        <v>35</v>
+        <v>73</v>
+      </c>
+      <c r="G87" t="s">
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J87" s="2">
-        <v>46341.62777777778</v>
+        <v>46342.25</v>
       </c>
       <c r="K87" s="2">
-        <v>46346.00277777778</v>
+        <v>46342.75</v>
       </c>
       <c r="L87" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4079,34 +4061,28 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
-      </c>
-      <c r="C88" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D88" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F88" t="s">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I88" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J88" s="2">
         <v>46342.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46342.75</v>
+        <v>46344.25</v>
       </c>
       <c r="L88" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4114,28 +4090,34 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F89" t="s">
-        <v>51</v>
+        <v>73</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J89" s="2">
-        <v>46342.25</v>
+        <v>46342.791666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46344.25</v>
+        <v>46343.75</v>
       </c>
       <c r="L89" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4143,34 +4125,31 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D90" t="s">
+        <v>190</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="F90" t="s">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="I90" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46342.791666666664</v>
+        <v>46343.208333333336</v>
       </c>
       <c r="K90" s="2">
-        <v>46343.75</v>
+        <v>46345.125</v>
       </c>
       <c r="L90" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4178,31 +4157,34 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D91" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F91" t="s">
-        <v>124</v>
+        <v>73</v>
+      </c>
+      <c r="G91" t="s">
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J91" s="2">
-        <v>46343.208333333336</v>
+        <v>46343.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46345.125</v>
+        <v>46343.75</v>
       </c>
       <c r="L91" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4210,28 +4192,28 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D92" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I92" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J92" s="2">
         <v>46343.25</v>
@@ -4240,7 +4222,7 @@
         <v>46343.75</v>
       </c>
       <c r="L92" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4248,34 +4230,31 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D93" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F93" t="s">
-        <v>80</v>
-      </c>
-      <c r="G93" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I93" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46343.25</v>
+        <v>46343.3125</v>
       </c>
       <c r="K93" s="2">
-        <v>46343.75</v>
+        <v>46346.604166666664</v>
       </c>
       <c r="L93" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4283,31 +4262,34 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F94" t="s">
-        <v>203</v>
+        <v>73</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J94" s="2">
-        <v>46343.3125</v>
+        <v>46343.791666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46346.604166666664</v>
+        <v>46344.75</v>
       </c>
       <c r="L94" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4315,10 +4297,10 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D95" t="s">
         <v>199</v>
@@ -4327,80 +4309,74 @@
         <v>200</v>
       </c>
       <c r="F95" t="s">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I95" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46343.791666666664</v>
+        <v>46344</v>
       </c>
       <c r="K95" s="2">
-        <v>46344.75</v>
+        <v>46346</v>
       </c>
       <c r="L95" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
-      </c>
-      <c r="C96" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>204</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F96" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46344</v>
+        <v>46344.083333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46346</v>
+        <v>46345.208333333336</v>
       </c>
       <c r="L96" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>56</v>
+      </c>
+      <c r="C97" t="s">
+        <v>57</v>
       </c>
       <c r="D97" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="F97" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46344.083333333336</v>
+        <v>46344.291666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46345.208333333336</v>
+        <v>46344.791666666664</v>
       </c>
       <c r="L97" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4408,28 +4384,28 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C98" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D98" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F98" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="J98" s="2">
-        <v>46344.291666666664</v>
+        <v>46344.625</v>
       </c>
       <c r="K98" s="2">
-        <v>46344.791666666664</v>
+        <v>46345.125</v>
       </c>
       <c r="L98" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4437,28 +4413,34 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C99" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D99" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F99" t="s">
         <v>73</v>
       </c>
-      <c r="F99" t="s">
-        <v>74</v>
+      <c r="G99" t="s">
+        <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J99" s="2">
-        <v>46344.625</v>
+        <v>46345.25</v>
       </c>
       <c r="K99" s="2">
-        <v>46345.125</v>
+        <v>46345.75</v>
       </c>
       <c r="L99" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4466,25 +4448,28 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
+      </c>
+      <c r="E100" s="1">
+        <v>89</v>
       </c>
       <c r="F100" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H100" t="s">
+        <v>205</v>
       </c>
       <c r="I100" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J100" s="2">
         <v>46345.25</v>
@@ -4493,77 +4478,71 @@
         <v>46345.75</v>
       </c>
       <c r="L100" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="D101" t="s">
-        <v>209</v>
-      </c>
-      <c r="E101" s="1">
-        <v>89</v>
+        <v>206</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F101" t="s">
-        <v>136</v>
-      </c>
-      <c r="G101" t="s">
-        <v>18</v>
-      </c>
-      <c r="H101" t="s">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="I101" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46345.25</v>
+        <v>46345.291666666664</v>
       </c>
       <c r="K101" s="2">
-        <v>46345.75</v>
+        <v>46346.166666666664</v>
       </c>
       <c r="L101" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F102" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46345.291666666664</v>
+        <v>46345.395833333336</v>
       </c>
       <c r="K102" s="2">
-        <v>46346.166666666664</v>
+        <v>46349.1875</v>
       </c>
       <c r="L102" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4574,19 +4553,19 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J103" s="2">
         <v>46345.395833333336</v>
@@ -4595,123 +4574,123 @@
         <v>46349.1875</v>
       </c>
       <c r="L103" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="D104" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46345.395833333336</v>
+        <v>46346.23333333333</v>
       </c>
       <c r="K104" s="2">
-        <v>46349.1875</v>
+        <v>46347.275000000001</v>
       </c>
       <c r="L104" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="C105" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="D105" t="s">
-        <v>215</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="F105" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46346.23333333333</v>
+        <v>46346.333333333336</v>
       </c>
       <c r="K105" s="2">
-        <v>46347.275000000001</v>
+        <v>46346.833333333336</v>
       </c>
       <c r="L105" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B106" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C106" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D106" t="s">
-        <v>87</v>
+        <v>212</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="F106" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46346.333333333336</v>
+        <v>46346.395833333336</v>
       </c>
       <c r="K106" s="2">
-        <v>46346.833333333336</v>
+        <v>46347.604166666664</v>
       </c>
       <c r="L106" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F107" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J107" s="2">
         <v>46346.395833333336</v>
@@ -4720,91 +4699,91 @@
         <v>46347.604166666664</v>
       </c>
       <c r="L107" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D108" t="s">
-        <v>217</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>218</v>
+        <v>87</v>
       </c>
       <c r="F108" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J108" s="2">
-        <v>46346.395833333336</v>
+        <v>46346.541666666664</v>
       </c>
       <c r="K108" s="2">
-        <v>46347.604166666664</v>
+        <v>46347.041666666664</v>
       </c>
       <c r="L108" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B109" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D109" t="s">
-        <v>94</v>
+        <v>214</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="F109" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J109" s="2">
-        <v>46346.541666666664</v>
+        <v>46346.583333333336</v>
       </c>
       <c r="K109" s="2">
-        <v>46347.041666666664</v>
+        <v>46348.083333333336</v>
       </c>
       <c r="L109" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J110" s="2">
         <v>46346.583333333336</v>
@@ -4813,39 +4792,7 @@
         <v>46348.083333333336</v>
       </c>
       <c r="L110" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12">
-      <c r="A111" t="s">
-        <v>24</v>
-      </c>
-      <c r="B111" t="s">
-        <v>25</v>
-      </c>
-      <c r="C111" t="s">
-        <v>84</v>
-      </c>
-      <c r="D111" t="s">
-        <v>219</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F111" t="s">
-        <v>203</v>
-      </c>
-      <c r="I111" t="s">
-        <v>19</v>
-      </c>
-      <c r="J111" s="2">
-        <v>46346.583333333336</v>
-      </c>
-      <c r="K111" s="2">
-        <v>46348.083333333336</v>
-      </c>
-      <c r="L111" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4857,6 +4804,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4864,7 +4817,7 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4873,7 +4826,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5011,24 +4964,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>